--- a/userlogin.xlsx
+++ b/userlogin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Customer_Freeze\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Churn_Monitoring_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBED63B5-6894-4596-84C5-9CEBEA796B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988A3402-A09F-4E45-AD02-EDDD7FF6D860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CB2E5262-B3CD-4402-819F-1DD8123238D2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>username</t>
   </si>
@@ -66,6 +66,24 @@
   </si>
   <si>
     <t>full name</t>
+  </si>
+  <si>
+    <t>aria.widura</t>
+  </si>
+  <si>
+    <t>Aria Widura</t>
+  </si>
+  <si>
+    <t>retno.wulan</t>
+  </si>
+  <si>
+    <t>Retno Wulan Dari</t>
+  </si>
+  <si>
+    <t>Elyza</t>
+  </si>
+  <si>
+    <t>elyza</t>
   </si>
 </sst>
 </file>
@@ -437,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE81CCA-941D-4BEF-AAFF-E40F40911A99}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -489,6 +507,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
